--- a/product_upload/packages/64/file.xlsx
+++ b/product_upload/packages/64/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -838,6 +843,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>HEXAXIM VACCINE</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-109B4096C30E</t>
         </is>
       </c>
@@ -861,7 +871,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1016,6 +1026,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ELNASO 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-C75D66ED0D44</t>
         </is>
       </c>
@@ -1039,7 +1054,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1198,6 +1213,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ONDANSETRON MEDIS 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-138A1E89693C</t>
         </is>
       </c>
@@ -1221,7 +1241,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1372,6 +1392,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>PATANOL 0.1% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-829BF1F7324C</t>
         </is>
       </c>
@@ -1395,7 +1420,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1556,6 +1581,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>SILOMES 400 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-0F387375EC02</t>
         </is>
       </c>
@@ -1579,7 +1609,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1738,6 +1768,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>BETOLINA 5MG/ML INJECTION</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-06596F3F84D7</t>
         </is>
       </c>
@@ -1761,7 +1796,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1916,6 +1951,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-1C6485CCFB1A</t>
         </is>
       </c>
@@ -1939,7 +1979,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2094,6 +2134,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>OLSAR 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-86370F6E2A24</t>
         </is>
       </c>
@@ -2117,7 +2162,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2276,6 +2321,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>OLSAR 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-CE27BC46A978</t>
         </is>
       </c>
@@ -2299,7 +2349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2458,6 +2508,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>LICAN 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-CC66CAFB42F3</t>
         </is>
       </c>
@@ -2481,7 +2536,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2636,6 +2691,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>TAZMERON 15MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-D9A4EC6E14F0</t>
         </is>
       </c>
@@ -2659,7 +2719,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2818,6 +2878,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>TAZMERON 30MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-B2ED0EE99F29</t>
         </is>
       </c>
@@ -2841,7 +2906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2996,6 +3061,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>TAZMERON 45MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-5693AF321A30</t>
         </is>
       </c>
@@ -3019,7 +3089,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3174,6 +3244,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-176D68B37A26</t>
         </is>
       </c>
@@ -3197,7 +3272,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3348,6 +3423,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-DC25544D0FCC</t>
         </is>
       </c>
@@ -3371,7 +3451,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3526,6 +3606,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>DESCOVY 200MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-664709B833A7</t>
         </is>
       </c>
@@ -3549,7 +3634,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3704,6 +3789,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ISONIAZID 300MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-B7929CB0DD26</t>
         </is>
       </c>
@@ -3727,7 +3817,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3882,6 +3972,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CYBELLE FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-2FE8AF0FF21D</t>
         </is>
       </c>
@@ -3905,7 +4000,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4060,6 +4155,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ACCEPT 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-67552324B113</t>
         </is>
       </c>
@@ -4083,7 +4183,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4238,6 +4338,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SABRIL 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-63D2BBAD2243</t>
         </is>
       </c>
@@ -4261,7 +4366,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4422,6 +4527,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>D-Seul 2000 I.U ORAL SOLUTION DROPS</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-74F8CD0EA434</t>
         </is>
       </c>
@@ -4445,7 +4555,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4602,6 +4712,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CRESEMBA 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-44B3FDFD6C6D</t>
         </is>
       </c>
@@ -4625,7 +4740,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4784,6 +4899,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>GLACERA PLUS 15MG/500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-0C9AB873E6DA</t>
         </is>
       </c>
@@ -4807,7 +4927,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4962,6 +5082,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-82333B113C1F</t>
         </is>
       </c>
@@ -4985,7 +5110,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5144,6 +5269,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>GLACERA PLUS 15MG/850MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-C93F03551075</t>
         </is>
       </c>
@@ -5167,7 +5297,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5326,6 +5456,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LEVOBAT 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-6209ADD708FA</t>
         </is>
       </c>
@@ -5349,7 +5484,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5504,6 +5639,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>TEDO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-044BA51EF56F</t>
         </is>
       </c>
@@ -5527,7 +5667,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5682,6 +5822,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-8ECD51BA5C18</t>
         </is>
       </c>
@@ -5705,7 +5850,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5864,6 +6009,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>BELARA 0.03MG/2MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-01074E1A9E79</t>
         </is>
       </c>
@@ -5887,7 +6037,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6046,6 +6196,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-2D2A7E386F8C</t>
         </is>
       </c>
@@ -6069,7 +6224,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6220,6 +6375,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>BUFOMIX 160/4.5MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-A6255A2B9721</t>
         </is>
       </c>
@@ -6243,7 +6403,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6394,6 +6554,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>BUFOMIX 320/9MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-F0A6D297D9B6</t>
         </is>
       </c>
@@ -6417,7 +6582,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6572,6 +6737,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-50C3C84A2631</t>
         </is>
       </c>
@@ -6595,7 +6765,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6746,6 +6916,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CYERO 25/15 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-03077A1BB184</t>
         </is>
       </c>
@@ -6769,7 +6944,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6932,6 +7107,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>STRATTERA 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-739D2DC07DB5</t>
         </is>
       </c>
@@ -6955,7 +7135,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7114,6 +7294,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>XYLOCAIN 10% SPRAY 10MG-DOSE</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-8B34121439FD</t>
         </is>
       </c>
@@ -7137,7 +7322,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7288,6 +7473,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CYERO 25/30 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-34F9824F73CC</t>
         </is>
       </c>
@@ -7311,7 +7501,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7470,6 +7660,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ROMACIN POWDER FOR ORAL/RECTAL Suspension</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-1D6EF0B4B6B3</t>
         </is>
       </c>
@@ -7493,7 +7688,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7652,6 +7847,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>CORREX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-C59A43782938</t>
         </is>
       </c>
@@ -7675,7 +7875,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7830,6 +8030,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ISONIAZID 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-49DF62035B69</t>
         </is>
       </c>
@@ -7853,7 +8058,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8008,6 +8213,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>LUTTAGEN 0.075MG/0.03MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-E5E1B5DED3FD</t>
         </is>
       </c>
@@ -8031,7 +8241,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8186,6 +8396,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 40 mg/25 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-E604D91F2695</t>
         </is>
       </c>
@@ -8209,7 +8424,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8372,6 +8587,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>TRIX 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-FD776DC23E03</t>
         </is>
       </c>
@@ -8395,7 +8615,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8550,6 +8770,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-4EC0F08CDDB8</t>
         </is>
       </c>
@@ -8573,7 +8798,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8736,6 +8961,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>QUZAL 25 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-BD2D6DC08DCE</t>
         </is>
       </c>
@@ -8759,7 +8989,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8914,6 +9144,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>HAIRAL 2% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-51B6A54C829D</t>
         </is>
       </c>
@@ -8937,7 +9172,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9096,6 +9331,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>QUZAL 100 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-C0A75707A270</t>
         </is>
       </c>
@@ -9119,7 +9359,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9274,6 +9514,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>PADO 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-D498FD343688</t>
         </is>
       </c>
@@ -9297,7 +9542,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9452,6 +9697,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>COVATEL 40MG/10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-7FCD49382C77</t>
         </is>
       </c>
@@ -9475,7 +9725,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9634,6 +9884,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>COVATEL</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-76C17BC59744</t>
         </is>
       </c>
@@ -9657,7 +9912,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9816,6 +10071,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>QUZAL 200 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-ECD61ADC38CA</t>
         </is>
       </c>
@@ -9839,7 +10099,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9998,6 +10258,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>GLADOS MET 15/850 TABLETS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-327F27DF1258</t>
         </is>
       </c>
@@ -10021,7 +10286,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10180,6 +10445,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>GLADOS MET 15/500 TABLETS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-4F1180F2D108</t>
         </is>
       </c>
@@ -10203,7 +10473,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10362,6 +10632,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Relif 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-DB70E25D1810</t>
         </is>
       </c>
@@ -10385,7 +10660,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10540,6 +10815,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Relif 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-89FEA6E9CC2C</t>
         </is>
       </c>
@@ -10563,7 +10843,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10722,6 +11002,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>IMATOX 4MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-CAC5EFA69B92</t>
         </is>
       </c>
@@ -10745,7 +11030,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10904,6 +11189,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>IMATOX 8MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-832BF7C0C71E</t>
         </is>
       </c>
@@ -10927,7 +11217,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11078,6 +11368,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t xml:space="preserve">NIZORTAN PLUS </t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-5DCD31166FF5</t>
         </is>
       </c>
@@ -11101,7 +11396,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11256,6 +11551,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-5ADD7E6533DC</t>
         </is>
       </c>
@@ -11279,7 +11579,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11434,6 +11734,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-3D7148C3C843</t>
         </is>
       </c>
@@ -11457,7 +11762,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11614,6 +11919,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CELLONA 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-B8CBADBD782A</t>
         </is>
       </c>
@@ -11637,7 +11947,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11800,6 +12110,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-6D03D2717C89</t>
         </is>
       </c>
@@ -11823,7 +12138,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -11974,6 +12289,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>PERTENSIO 125 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-433C72A58AB2</t>
         </is>
       </c>
@@ -11997,7 +12317,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12152,6 +12472,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>DEBROMU 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-F4E0BD8D61B6</t>
         </is>
       </c>
@@ -12175,7 +12500,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12338,6 +12663,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-257C6B2DC201</t>
         </is>
       </c>
@@ -12361,7 +12691,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12524,6 +12854,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>QUZAL 300 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-9097B9755B2B</t>
         </is>
       </c>
@@ -12547,7 +12882,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12710,6 +13045,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>STRATTERA 18MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-AF45386AFF05</t>
         </is>
       </c>
@@ -12733,7 +13073,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12892,6 +13232,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-0BD406238813</t>
         </is>
       </c>
@@ -12915,7 +13260,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13074,6 +13419,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-43B11651DB46</t>
         </is>
       </c>
@@ -13097,7 +13447,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13252,6 +13602,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>BRIVIACT 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-E6083D26425A</t>
         </is>
       </c>
@@ -13275,7 +13630,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13430,6 +13785,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>CORREX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-363AFD36EEEF</t>
         </is>
       </c>
@@ -13453,7 +13813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13612,6 +13972,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-26F29E1EB887</t>
         </is>
       </c>
@@ -13635,7 +14000,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13794,6 +14159,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-6EB4607B13CB</t>
         </is>
       </c>
@@ -13817,7 +14187,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -13980,6 +14350,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-1A00E07B1F06</t>
         </is>
       </c>
@@ -14003,7 +14378,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14162,6 +14537,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>MOTILONE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-D7F3BC540B78</t>
         </is>
       </c>
@@ -14185,7 +14565,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14344,6 +14724,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-74995A4A966A</t>
         </is>
       </c>
@@ -14367,7 +14752,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14530,6 +14915,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>RESPAL ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-E4828CBAADD2</t>
         </is>
       </c>
@@ -14553,7 +14943,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14708,6 +15098,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>ARCOXIA 120MG TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-C20D79ADA596</t>
         </is>
       </c>
@@ -14731,7 +15126,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14890,6 +15285,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>HAIRAL 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-FE26FF46D9B9</t>
         </is>
       </c>
@@ -14913,7 +15313,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15072,6 +15472,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>EDYST 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-74D56B520D05</t>
         </is>
       </c>
@@ -15095,7 +15500,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15254,6 +15659,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>MOXIQUIN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-A3927F75AAB8</t>
         </is>
       </c>
@@ -15277,7 +15687,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15428,6 +15838,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ZYROSA 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-05F52EA0AF3A</t>
         </is>
       </c>
@@ -15451,7 +15866,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15606,6 +16021,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>RUATINE 20MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-D66F8D69E27A</t>
         </is>
       </c>
@@ -15629,7 +16049,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15784,6 +16204,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ZYROSA 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-C5CB0EC7CEB3</t>
         </is>
       </c>
@@ -15807,7 +16232,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -15962,6 +16387,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>MOXIDAD CAPSULES 250MG</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-4DD34B1C9C5D</t>
         </is>
       </c>
@@ -15985,7 +16415,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16148,6 +16578,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>STRATTERA 25MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-01E8297154BB</t>
         </is>
       </c>
@@ -16171,7 +16606,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16326,6 +16761,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>BRIVIACT 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-7CC23FA0FC56</t>
         </is>
       </c>
@@ -16349,7 +16789,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16504,6 +16944,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>GLEPTAL 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-A5A9477CFC2B</t>
         </is>
       </c>
@@ -16527,7 +16972,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16690,6 +17135,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-1D2B7E65E565</t>
         </is>
       </c>
@@ -16713,7 +17163,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16872,6 +17322,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>XIBAX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-C261BBC2712C</t>
         </is>
       </c>
@@ -16895,7 +17350,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17058,6 +17513,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>NOVORAPID FLEXTOUCH 100U\ML</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-859485463034</t>
         </is>
       </c>
@@ -17081,7 +17541,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17240,6 +17700,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>ESCIPRA 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-6D8EE7B86FA9</t>
         </is>
       </c>
@@ -17263,7 +17728,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17426,6 +17891,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>STRATTERA 40MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-C17D17A5A694</t>
         </is>
       </c>
@@ -17449,7 +17919,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17604,6 +18074,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>BRIVIACT 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-6179C77F19E7</t>
         </is>
       </c>
@@ -17627,7 +18102,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17790,6 +18265,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-1E68EA903527</t>
         </is>
       </c>
@@ -17813,7 +18293,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -17972,6 +18452,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>SPASMOLYT 20 MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-B2C4CF1272A9</t>
         </is>
       </c>
@@ -17995,7 +18480,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18154,6 +18639,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>VOSEVI 400MG/100MG/100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-F51C4B88AB7C</t>
         </is>
       </c>
@@ -18177,7 +18667,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18336,6 +18826,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>TRAMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-68437C8323D5</t>
         </is>
       </c>
@@ -18359,7 +18854,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18522,6 +19017,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>STRATTERA 60MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-88DE9B6D4807</t>
         </is>
       </c>
@@ -18545,7 +19045,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18699,6 +19199,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>LOCOID LIPO CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-44619E3DA468</t>
         </is>
@@ -18715,7 +19220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18761,100 +19266,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18886,7 +19396,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18901,92 +19411,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-46905</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>450.19</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>652</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19018,7 +19533,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19033,92 +19548,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-22124</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>28.63</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>653</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19150,7 +19670,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19165,92 +19685,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-61122</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>461.87</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>654</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19282,7 +19807,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19297,92 +19822,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-75281</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>422.61</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>655</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19414,7 +19944,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19429,92 +19959,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-63811</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>278.53</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>656</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19546,7 +20081,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19561,92 +20096,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-65189</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>37.76</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>657</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19678,7 +20218,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19693,92 +20233,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-99822</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>404.59</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>658</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19810,7 +20355,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19825,92 +20370,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-58983</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>16.93</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>659</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19942,7 +20492,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19957,92 +20507,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-33929</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>338.62</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>660</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20074,7 +20629,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20089,92 +20644,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-45315</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>24.62</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>661</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20206,7 +20766,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20221,92 +20781,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-50826</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>10.79</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>662</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20323,7 +20888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20429,6 +20994,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20462,7 +21037,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20527,6 +21102,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-B7D787E9FA83</t>
         </is>
@@ -20561,7 +21146,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20626,6 +21211,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-0E853DD991C6</t>
         </is>
@@ -20660,7 +21255,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20725,6 +21320,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-4FBA1B5AB491</t>
         </is>
@@ -20759,7 +21364,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20824,6 +21429,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-87A5255FC4C5</t>
         </is>
@@ -20858,7 +21473,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -20923,6 +21538,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-3150F7D749ED</t>
         </is>
@@ -20957,7 +21582,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21022,6 +21647,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-912BF23FEB30</t>
         </is>
@@ -21056,7 +21691,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21121,6 +21756,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-94947B0F4579</t>
         </is>
@@ -21155,7 +21800,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21220,6 +21865,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-F487125F3C99</t>
         </is>
@@ -21254,7 +21909,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21319,6 +21974,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-04EC660DDE0B</t>
         </is>
@@ -21353,7 +22018,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21418,6 +22083,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-E6F070054089</t>
         </is>
@@ -21452,7 +22127,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21517,6 +22192,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-C900FA3A0211</t>
         </is>
@@ -21551,7 +22236,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21616,6 +22301,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-7F4755FDC346</t>
         </is>
@@ -21650,7 +22345,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21715,6 +22410,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-BC3E17638132</t>
         </is>
@@ -21749,7 +22454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21814,6 +22519,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-04C1F670B177</t>
         </is>
@@ -21848,7 +22563,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21913,6 +22628,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-41A3FCF6FEF5</t>
         </is>
@@ -21947,7 +22672,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22012,6 +22737,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-526978F681BA</t>
         </is>
@@ -22046,7 +22781,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22111,6 +22846,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-115EC59A235A</t>
         </is>
@@ -22145,7 +22890,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22210,6 +22955,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-D5DB3D600871</t>
         </is>
@@ -22244,7 +22999,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22309,6 +23064,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-0780DA25EFC5</t>
         </is>
@@ -22343,7 +23108,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22408,6 +23173,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-72241F894EF0</t>
         </is>

--- a/product_upload/packages/64/file.xlsx
+++ b/product_upload/packages/64/file.xlsx
@@ -686,8 +686,16 @@
           <t>6422875894-796-414457970865</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEXAXIM VACCINE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HEXAXIM VACCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -879,8 +887,16 @@
           <t>6807882578-520-289682095625</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELNASO 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ELNASO 0.05% NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1062,8 +1078,16 @@
           <t>1319365841-659-385769217490</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ONDANSETRON MEDIS 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ONDANSETRON MEDIS 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1249,8 +1273,16 @@
           <t>8088671254-843-042649693402</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PATANOL 0.1% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PATANOL 0.1% OPHTHALMIC SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1428,8 +1460,16 @@
           <t>0099856750-885-461525633487</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SILOMES 400 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SILOMES 400 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -1617,8 +1657,16 @@
           <t>3732420010-806-383048021978</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETOLINA 5MG/ML INJECTION</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BETOLINA 5MG/ML INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1804,8 +1852,16 @@
           <t>4783106501-336-826931691095</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1987,8 +2043,16 @@
           <t>5376104368-409-021718897570</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLSAR 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OLSAR 20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2170,8 +2234,16 @@
           <t>7557790682-084-322075492799</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLSAR 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OLSAR 40MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2357,8 +2429,16 @@
           <t>7357657876-497-601523384988</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LICAN 1% CREAM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LICAN 1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2544,8 +2624,16 @@
           <t>1914154999-489-846036545511</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAZMERON 15MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TAZMERON 15MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2727,8 +2815,16 @@
           <t>7522828238-895-495721193114</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAZMERON 30MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TAZMERON 30MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2914,8 +3010,16 @@
           <t>2797920742-877-091148587278</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAZMERON 45MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TAZMERON 45MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3097,8 +3201,16 @@
           <t>6180708330-818-762673006850</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3280,8 +3392,16 @@
           <t>9848521093-012-243288132826</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3459,8 +3579,16 @@
           <t>4450603979-829-713007565912</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESCOVY 200MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DESCOVY 200MG/10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3642,8 +3770,16 @@
           <t>9181497880-913-543708326101</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISONIAZID 300MG TABLET</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ISONIAZID 300MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3825,8 +3961,16 @@
           <t>5196626861-180-547639596802</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYBELLE FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CYBELLE FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4008,8 +4152,16 @@
           <t>3852224225-993-605832005122</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACCEPT 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ACCEPT 250MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4191,8 +4343,16 @@
           <t>3035932959-518-035587502254</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SABRIL 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SABRIL 500MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4374,8 +4534,16 @@
           <t>0399301401-383-699502090707</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-Seul 2000 I.U ORAL SOLUTION DROPS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D-Seul 2000 I.U ORAL SOLUTION DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -4563,8 +4731,16 @@
           <t>2355408771-284-156022623648</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CRESEMBA 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CRESEMBA 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -4748,8 +4924,16 @@
           <t>7902425828-296-912626588598</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLACERA PLUS 15MG/500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>GLACERA PLUS 15MG/500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4935,8 +5119,16 @@
           <t>7655621749-986-583152815505</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COXICEL 200 MG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>COXICEL 200 MG HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5118,8 +5310,16 @@
           <t>6419511024-681-286121179769</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLACERA PLUS 15MG/850MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>GLACERA PLUS 15MG/850MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5305,8 +5505,16 @@
           <t>3844016919-710-243067313596</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOBAT 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LEVOBAT 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5492,8 +5700,16 @@
           <t>7018820879-537-863337429072</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEDO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TEDO 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5675,8 +5891,16 @@
           <t>0353578608-999-789997090625</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COXICEL 200 MG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COXICEL 200 MG HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5858,8 +6082,16 @@
           <t>1587380326-754-191304578826</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BELARA 0.03MG/2MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BELARA 0.03MG/2MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6045,8 +6277,16 @@
           <t>5135371075-632-273471008601</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COXICEL 200 MG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COXICEL 200 MG HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6232,8 +6472,16 @@
           <t>8536876612-318-580417336014</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUFOMIX 160/4.5MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>BUFOMIX 160/4.5MCG EASYHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6411,8 +6659,16 @@
           <t>3396725971-138-213852796581</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUFOMIX 320/9MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>BUFOMIX 320/9MCG EASYHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6590,8 +6846,16 @@
           <t>4957851842-702-664921239691</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6773,8 +7037,16 @@
           <t>0701644031-439-070928832730</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYERO 25/15 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CYERO 25/15 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -6952,8 +7224,16 @@
           <t>8361556703-829-384440912632</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>STRATTERA 10MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7143,8 +7423,16 @@
           <t>6099902510-596-443282584071</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XYLOCAIN 10% SPRAY 10MG-DOSE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>XYLOCAIN 10% SPRAY 10MG-DOSE detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7330,8 +7618,16 @@
           <t>5343950413-438-349027337989</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYERO 25/30 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CYERO 25/30 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7509,8 +7805,16 @@
           <t>1364589273-196-363205930404</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROMACIN POWDER FOR ORAL/RECTAL Suspension</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ROMACIN POWDER FOR ORAL/RECTAL Suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7696,8 +8000,16 @@
           <t>5135703514-720-849802602289</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CORREX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CORREX 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7883,8 +8195,16 @@
           <t>7867168945-529-301386331732</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISONIAZID 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ISONIAZID 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8066,8 +8386,16 @@
           <t>6832911495-117-603056100321</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUTTAGEN 0.075MG/0.03MG TABLET</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>LUTTAGEN 0.075MG/0.03MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8249,8 +8577,16 @@
           <t>3090472125-845-628874537683</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 40 mg/25 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 40 mg/25 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8432,8 +8768,16 @@
           <t>4794262122-253-700378130675</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIX 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TRIX 200 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8623,8 +8967,16 @@
           <t>8898567932-607-233148453919</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8806,8 +9158,16 @@
           <t>6080804668-170-493888711769</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 25 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>QUZAL 25 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -8997,8 +9357,16 @@
           <t>7718509377-835-551718165653</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRAL 2% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>HAIRAL 2% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9180,8 +9548,16 @@
           <t>5316641209-989-845317193258</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 100 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>QUZAL 100 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9367,8 +9743,16 @@
           <t>8816915105-918-355922236515</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PADO 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PADO 20MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9550,8 +9934,16 @@
           <t>0529339441-761-815992847210</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL 40MG/10MG TABLET</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>COVATEL 40MG/10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9733,8 +10125,16 @@
           <t>4483975446-568-416158172653</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COVATEL detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -9920,8 +10320,16 @@
           <t>3513913475-163-392127035598</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 200 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>QUZAL 200 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10107,8 +10515,16 @@
           <t>8398731781-113-310841791434</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLADOS MET 15/850 TABLETS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>GLADOS MET 15/850 TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10294,8 +10710,16 @@
           <t>3422770993-025-547913896081</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLADOS MET 15/500 TABLETS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>GLADOS MET 15/500 TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10481,8 +10905,16 @@
           <t>0183118584-871-341202825519</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Relif 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Relif 100 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10668,8 +11100,16 @@
           <t>4245609054-859-529414081234</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Relif 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Relif 200 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10851,8 +11291,16 @@
           <t>3808784339-675-723544387333</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IMATOX 4MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>IMATOX 4MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11038,8 +11486,16 @@
           <t>6939769107-034-903101475784</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IMATOX 8MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>IMATOX 8MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11225,8 +11681,16 @@
           <t>9048207745-523-697025436149</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11404,8 +11868,16 @@
           <t>1483048930-208-069011864886</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11587,8 +12059,16 @@
           <t>6822870840-885-653568621069</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11770,8 +12250,16 @@
           <t>8744682447-154-150190419346</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELLONA 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CELLONA 500 mg F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -11955,8 +12443,16 @@
           <t>2462611630-991-934356092503</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12146,8 +12642,16 @@
           <t>2751923864-225-392602669948</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PERTENSIO 125 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PERTENSIO 125 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12325,8 +12829,16 @@
           <t>7179368314-949-153631686347</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEBROMU 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DEBROMU 40MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12508,8 +13020,16 @@
           <t>9205532543-494-151544386834</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12699,8 +13219,16 @@
           <t>3901668092-716-604999342117</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 300 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>QUZAL 300 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -12890,8 +13418,16 @@
           <t>5246067311-950-795166594052</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 18MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>STRATTERA 18MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13081,8 +13617,16 @@
           <t>6410360071-814-421149310407</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13268,8 +13812,16 @@
           <t>6531610742-932-918708866195</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>QUZAL 400 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13455,8 +14007,16 @@
           <t>8701721240-958-612818164645</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>BRIVIACT 50MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13638,8 +14198,16 @@
           <t>2226459713-282-416553476442</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CORREX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CORREX 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13821,8 +14389,16 @@
           <t>0770604045-185-938098674972</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>COMBIWAVE detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14008,8 +14584,16 @@
           <t>3420171840-654-928001879629</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14195,8 +14779,16 @@
           <t>2713524299-693-358224678102</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>QUZAL 400 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14386,8 +14978,16 @@
           <t>9013632582-920-102824385520</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOTILONE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MOTILONE 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14573,8 +15173,16 @@
           <t>3930048978-058-653618740011</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14760,8 +15368,16 @@
           <t>7087892394-506-019783205637</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESPAL ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>RESPAL ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -14951,8 +15567,16 @@
           <t>2248117408-003-169813184451</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARCOXIA 120MG TAB</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ARCOXIA 120MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15134,8 +15758,16 @@
           <t>7476692978-659-278677349967</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRAL 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>HAIRAL 5% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15321,8 +15953,16 @@
           <t>3333064729-869-934745960935</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EDYST 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>EDYST 20 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15508,8 +16148,16 @@
           <t>2254756377-262-539671691904</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXIQUIN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>MOXIQUIN 400MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15695,8 +16343,16 @@
           <t>7562902930-204-075738112826</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYROSA 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ZYROSA 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -15874,8 +16530,16 @@
           <t>9286225362-862-003901221848</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RUATINE 20MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>RUATINE 20MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16057,8 +16721,16 @@
           <t>0777434401-170-352001612019</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYROSA 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ZYROSA 20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16240,8 +16912,16 @@
           <t>1993002751-136-179425122434</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXIDAD CAPSULES 250MG</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>MOXIDAD CAPSULES 250MG detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16423,8 +17103,16 @@
           <t>8891048992-971-040689103878</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 25MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>STRATTERA 25MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16614,8 +17302,16 @@
           <t>2829948059-506-203497911303</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BRIVIACT 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16797,8 +17493,16 @@
           <t>3631594692-857-258209948099</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEPTAL 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>GLEPTAL 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -16980,8 +17684,16 @@
           <t>1518094641-907-873309796235</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>COMBIWAVE detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17171,8 +17883,16 @@
           <t>2326268041-392-036915172756</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XIBAX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>XIBAX 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17358,8 +18078,16 @@
           <t>9363213559-961-252344702226</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVORAPID FLEXTOUCH 100U\ML</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>NOVORAPID FLEXTOUCH 100U\ML detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17549,8 +18277,16 @@
           <t>7433696933-669-118405446605</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESCIPRA 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ESCIPRA 10MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17736,8 +18472,16 @@
           <t>0092276516-514-564114813579</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 40MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>STRATTERA 40MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -17927,8 +18671,16 @@
           <t>5722854307-504-560846153018</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>BRIVIACT 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18110,8 +18862,16 @@
           <t>1680139610-118-347991211214</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>COMBIWAVE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18301,8 +19061,16 @@
           <t>3006686477-167-171847625033</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPASMOLYT 20 MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>SPASMOLYT 20 MG COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18488,8 +19256,16 @@
           <t>4302163400-916-574763419796</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VOSEVI 400MG/100MG/100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>VOSEVI 400MG/100MG/100MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18675,8 +19451,16 @@
           <t>3523723421-083-233694199344</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRAMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TRAMAL 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18862,8 +19646,16 @@
           <t>6586572355-856-130606281500</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 60MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>STRATTERA 60MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19053,8 +19845,16 @@
           <t>1779565904-411-463022393200</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCOID LIPO CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LOCOID LIPO CREAM 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/64/file.xlsx
+++ b/product_upload/packages/64/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21688,7 +21688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21769,40 +21769,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21880,38 +21885,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>29.31</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-B7D787E9FA83</t>
         </is>
@@ -21989,38 +21999,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>443.99</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-0E853DD991C6</t>
         </is>
@@ -22098,38 +22113,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>207.87</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-4FBA1B5AB491</t>
         </is>
@@ -22207,38 +22227,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>91.70999999999999</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-87A5255FC4C5</t>
         </is>
@@ -22316,38 +22341,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>48.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-3150F7D749ED</t>
         </is>
@@ -22425,38 +22455,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>426.32</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-912BF23FEB30</t>
         </is>
@@ -22534,38 +22569,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>69.44</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-94947B0F4579</t>
         </is>
@@ -22643,38 +22683,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>198.68</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-F487125F3C99</t>
         </is>
@@ -22752,38 +22797,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>300.91</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-04EC660DDE0B</t>
         </is>
@@ -22861,38 +22911,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>434.79</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-E6F070054089</t>
         </is>
@@ -22970,38 +23025,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>342.21</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-C900FA3A0211</t>
         </is>
@@ -23079,38 +23139,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>52.75</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-7F4755FDC346</t>
         </is>
@@ -23188,38 +23253,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>452.98</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-BC3E17638132</t>
         </is>
@@ -23297,38 +23367,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>72.93000000000001</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-04C1F670B177</t>
         </is>
@@ -23406,38 +23481,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>392.19</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-41A3FCF6FEF5</t>
         </is>
@@ -23515,38 +23595,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>200.53</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-526978F681BA</t>
         </is>
@@ -23624,38 +23709,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>289.72</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-115EC59A235A</t>
         </is>
@@ -23733,38 +23823,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>28.43</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-D5DB3D600871</t>
         </is>
@@ -23842,38 +23937,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>292.98</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-0780DA25EFC5</t>
         </is>
@@ -23951,38 +24051,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>196.92</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-72241F894EF0</t>
         </is>
